--- a/Plan.xlsx
+++ b/Plan.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSF\Project 4week\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127BB2C2-DEF6-42E7-A1EE-9C33FE7E251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{184FCEDC-090A-4386-A1B2-715B7A33DF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="1" r:id="rId1"/>
     <sheet name="Kế hoạch 4 tuần" sheetId="5" r:id="rId2"/>
     <sheet name="Test scenarios" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="453">
   <si>
     <t>V-MARKET — THIẾT LẬP KẾ HOẠCH</t>
   </si>
@@ -49,6 +52,9 @@
     <t>Ngày bắt đầu (thứ Hai)</t>
   </si>
   <si>
+    <t>Thời lượng</t>
+  </si>
+  <si>
     <t>4 tuần / 20 ngày làm việc</t>
   </si>
   <si>
@@ -106,42 +112,66 @@
     <t>Ghi chú</t>
   </si>
   <si>
+    <t>Nền tảng</t>
+  </si>
+  <si>
+    <t>Khởi tạo dự án, cấu hình môi trường, đăng nhập và hai vai trò</t>
+  </si>
+  <si>
+    <t>Buyer và Seller đăng nhập độc lập</t>
+  </si>
+  <si>
     <t>P0</t>
   </si>
   <si>
+    <t>Ngày 1</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Hai phiên đăng nhập</t>
+  </si>
+  <si>
+    <t>Có tài khoản seed cho buyer, seller A, seller B</t>
+  </si>
+  <si>
+    <t>Tích hợp V-App</t>
+  </si>
+  <si>
+    <t>Đọc tài liệu và xác định các điểm tích hợp cần mô phỏng: đăng nhập, thông tin người dùng, phiên thanh toán và kết quả thanh toán</t>
+  </si>
+  <si>
+    <t>Hoàn thành danh sách API, dữ liệu vào/ra và sơ đồ luồng giữa MiniApp, V-Market Backend và Mock V-App</t>
+  </si>
+  <si>
+    <t>Ngày 2</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Chốt API, API hoạt động</t>
+  </si>
+  <si>
+    <t>Không xây lại toàn bộ V-App; chỉ mô phỏng các chức năng V-Market sử dụng</t>
+  </si>
+  <si>
+    <t>Seller</t>
+  </si>
+  <si>
+    <t>Tạo và quản lý cửa hàng</t>
+  </si>
+  <si>
+    <t>Seller tạo/chỉnh sửa được shop và chỉ quản lý shop của mình</t>
+  </si>
+  <si>
+    <t>Ngày 3</t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
-    <t>Nền tảng</t>
-  </si>
-  <si>
-    <t>Khởi tạo dự án, cấu hình môi trường, đăng nhập và hai vai trò</t>
-  </si>
-  <si>
-    <t>Buyer và Seller đăng nhập độc lập</t>
-  </si>
-  <si>
-    <t>Ngày 1</t>
-  </si>
-  <si>
-    <t>Hai phiên đăng nhập</t>
-  </si>
-  <si>
-    <t>Có tài khoản seed cho buyer, seller A, seller B</t>
-  </si>
-  <si>
-    <t>Seller</t>
-  </si>
-  <si>
-    <t>Tạo và quản lý cửa hàng</t>
-  </si>
-  <si>
-    <t>Seller tạo/chỉnh sửa được shop và chỉ quản lý shop của mình</t>
-  </si>
-  <si>
-    <t>Ngày 2</t>
-  </si>
-  <si>
     <t>Shop hoạt động</t>
   </si>
   <si>
@@ -157,7 +187,7 @@
     <t>Seller đăng được sản phẩm có màu/size hoặc phiên bản</t>
   </si>
   <si>
-    <t>Ngày 3</t>
+    <t>Ngày 4</t>
   </si>
   <si>
     <t>Sản phẩm hợp lệ</t>
@@ -175,7 +205,7 @@
     <t>Buyer nhìn thấy sản phẩm vừa đăng</t>
   </si>
   <si>
-    <t>Ngày 4</t>
+    <t>Ngày 5</t>
   </si>
   <si>
     <t>Checkpoint tuần 1</t>
@@ -193,9 +223,6 @@
     <t>Thêm/xóa/sửa số lượng và nhóm đúng theo từng shop</t>
   </si>
   <si>
-    <t>Ngày 5</t>
-  </si>
-  <si>
     <t>Giỏ hàng đa shop</t>
   </si>
   <si>
@@ -460,21 +487,6 @@
     <t>Có video hoặc ảnh dự phòng nếu môi trường gặp sự cố</t>
   </si>
   <si>
-    <t>Thời lượng</t>
-  </si>
-  <si>
-    <t>Tích hợp V-App</t>
-  </si>
-  <si>
-    <t>Đọc tài liệu và xác định các điểm tích hợp cần mô phỏng: đăng nhập, thông tin người dùng, phiên thanh toán và kết quả thanh toán</t>
-  </si>
-  <si>
-    <t>Hoàn thành danh sách API, dữ liệu vào/ra và sơ đồ luồng giữa MiniApp, V-Market Backend và Mock V-App</t>
-  </si>
-  <si>
-    <t>Không xây lại toàn bộ V-App; chỉ mô phỏng các chức năng V-Market sử dụng</t>
-  </si>
-  <si>
     <t>V-MARKET — TEST MATRIX</t>
   </si>
   <si>
@@ -1385,18 +1397,14 @@
   </si>
   <si>
     <t>Xác định điểm gãy và hệ thống phục hồi</t>
-  </si>
-  <si>
-    <t>Chốt API, API hoạt động</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1485,49 +1493,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1685,87 +1651,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1783,29 +1732,39 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2926,6 +2885,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3118,73 +3081,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27" style="3" customWidth="1"/>
-    <col min="2" max="2" width="56.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="56.19921875" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="38"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" ht="21.95" customHeight="1"/>
-    <row r="3" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:4" ht="21.9" customHeight="1"/>
+    <row r="3" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="35">
         <v>46225</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A5" s="34" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="B5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A7" s="34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="B7" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="21.9" customHeight="1">
+      <c r="A8" s="34" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="21.95" customHeight="1"/>
-    <row r="10" spans="1:4" ht="21.95" customHeight="1"/>
-    <row r="11" spans="1:4" ht="21.95" customHeight="1"/>
+      <c r="B8" s="36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21.9" customHeight="1"/>
+    <row r="10" spans="1:4" ht="21.9" customHeight="1"/>
+    <row r="11" spans="1:4" ht="21.9" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
@@ -3197,896 +3160,896 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737A32AE-25EB-48DD-B91D-ADFB2344FA77}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="30.375" defaultRowHeight="45" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="30.3984375" defaultRowHeight="45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A1" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="A1" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="45" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="B2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="C2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="D2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="F2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="G2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="H2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="I2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="J2" s="19" t="s">
         <v>22</v>
       </c>
+      <c r="K2" s="20" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="45" customHeight="1">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="1:11" ht="45" customHeight="1">
-      <c r="A4" s="22">
+      <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="5">
         <f>INFO!$B$4+INT((A4-1)/5)*7+MOD(A4-1,5)</f>
         <v>46225</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="13">
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="6">
         <f>IF(H4="Done",100,IF(H4="In Progress",50,IF(H4="Blocked",25,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="K4" s="16" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="64.5" customHeight="1">
-      <c r="A5" s="22">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="5">
         <f>INFO!$B$4+INT((A5-1)/5)*7+MOD(A5-1,5)</f>
         <v>46226</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="13">
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="6">
         <f t="shared" ref="I5" si="0">IF(H5="Done",100,IF(H5="In Progress",50,IF(H5="Blocked",25,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>450</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>145</v>
+        <v>50</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" customHeight="1">
-      <c r="A6" s="22">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="5">
         <f>INFO!$B$4+INT((A6-1)/5)*7+MOD(A6-1,5)</f>
         <v>46227</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="C6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="13">
+      <c r="E6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="6">
         <f t="shared" ref="I6:I23" si="1">IF(H6="Done",100,IF(H6="In Progress",50,IF(H6="Blocked",25,0)))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>36</v>
+      <c r="J6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="45" customHeight="1">
-      <c r="A7" s="22">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="5">
         <f>INFO!$B$4+INT((A7-1)/5)*7+MOD(A7-1,5)</f>
         <v>46228</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="13">
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>42</v>
+      <c r="J7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1">
-      <c r="A8" s="22">
+      <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="8">
         <f>INFO!$B$4+INT((A8-1)/5)*7+MOD(A8-1,5)</f>
         <v>46229</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="I8" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>48</v>
+      <c r="J8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" customHeight="1">
-      <c r="A9" s="28">
+      <c r="A9" s="21">
         <v>6</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="11">
         <f>INFO!$B$4+INT((A9-1)/5)*7+MOD(A9-1,5)</f>
         <v>46232</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="19">
+      <c r="C9" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>54</v>
+      <c r="J9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="5">
         <f>INFO!$B$4+INT((A10-1)/5)*7+MOD(A10-1,5)</f>
         <v>46233</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="13">
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>60</v>
+      <c r="J10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="5">
         <f>INFO!$B$4+INT((A11-1)/5)*7+MOD(A11-1,5)</f>
         <v>46234</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="13">
+      <c r="C11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>66</v>
+      <c r="J11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" customHeight="1">
-      <c r="A12" s="22">
+      <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="5">
         <f>INFO!$B$4+INT((A12-1)/5)*7+MOD(A12-1,5)</f>
         <v>46235</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="C12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>72</v>
+      <c r="J12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1">
-      <c r="A13" s="24">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="8">
         <f>INFO!$B$4+INT((A13-1)/5)*7+MOD(A13-1,5)</f>
         <v>46236</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="16">
+      <c r="C13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>78</v>
+      <c r="J13" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="45" customHeight="1">
-      <c r="A14" s="28">
+      <c r="A14" s="21">
         <v>11</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="11">
         <f>INFO!$B$4+INT((A14-1)/5)*7+MOD(A14-1,5)</f>
         <v>46239</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="19">
+      <c r="C14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>84</v>
+      <c r="J14" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="15">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="5">
         <f>INFO!$B$4+INT((A15-1)/5)*7+MOD(A15-1,5)</f>
         <v>46240</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="13">
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>90</v>
+      <c r="J15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="15">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="5">
         <f>INFO!$B$4+INT((A16-1)/5)*7+MOD(A16-1,5)</f>
         <v>46241</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="13">
+      <c r="C16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>96</v>
+      <c r="J16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="45" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="15">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="5">
         <f>INFO!$B$4+INT((A17-1)/5)*7+MOD(A17-1,5)</f>
         <v>46242</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="13">
+      <c r="C17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>103</v>
+      <c r="J17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="45" customHeight="1">
-      <c r="A18" s="24">
+      <c r="A18" s="17">
         <v>15</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="8">
         <f>INFO!$B$4+INT((A18-1)/5)*7+MOD(A18-1,5)</f>
         <v>46243</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="16">
+      <c r="C18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>109</v>
+      <c r="J18" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="45" customHeight="1">
-      <c r="A19" s="28">
+      <c r="A19" s="21">
         <v>16</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="11">
         <f>INFO!$B$4+INT((A19-1)/5)*7+MOD(A19-1,5)</f>
         <v>46246</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="19">
+      <c r="C19" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="K19" s="29" t="s">
-        <v>115</v>
+      <c r="J19" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="45" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="5">
         <f>INFO!$B$4+INT((A20-1)/5)*7+MOD(A20-1,5)</f>
         <v>46247</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="13">
+      <c r="C20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>122</v>
+      <c r="J20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="45" customHeight="1">
-      <c r="A21" s="22">
+      <c r="A21" s="15">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="5">
         <f>INFO!$B$4+INT((A21-1)/5)*7+MOD(A21-1,5)</f>
         <v>46248</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="13">
+      <c r="C21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>128</v>
+      <c r="J21" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1">
-      <c r="A22" s="22">
+      <c r="A22" s="15">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="5">
         <f>INFO!$B$4+INT((A22-1)/5)*7+MOD(A22-1,5)</f>
         <v>46249</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="13">
+      <c r="C22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>134</v>
+      <c r="J22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="45" customHeight="1">
-      <c r="A23" s="24">
+      <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="8">
         <f>INFO!$B$4+INT((A23-1)/5)*7+MOD(A23-1,5)</f>
         <v>46250</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="16">
+      <c r="C23" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>140</v>
+      <c r="J23" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="45" customHeight="1">
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
     </row>
     <row r="27" spans="1:15" ht="45" customHeight="1">
-      <c r="E27" s="30"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
     </row>
     <row r="28" spans="1:15" ht="45" customHeight="1">
-      <c r="E28" s="30"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
     </row>
     <row r="29" spans="1:15" ht="45" customHeight="1">
-      <c r="E29" s="30"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
     </row>
     <row r="30" spans="1:15" ht="45" customHeight="1">
-      <c r="E30" s="30"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
     </row>
     <row r="31" spans="1:15" ht="45" customHeight="1">
-      <c r="E31" s="30"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4171,2608 +4134,2608 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275A1A88-33A2-401C-9748-06882D004064}">
   <dimension ref="A1:M199"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="13" style="35" customWidth="1"/>
-    <col min="2" max="2" width="28" style="35" customWidth="1"/>
-    <col min="3" max="3" width="16" style="35" customWidth="1"/>
-    <col min="4" max="4" width="10" style="35" customWidth="1"/>
-    <col min="5" max="5" width="38" style="35" customWidth="1"/>
-    <col min="6" max="6" width="30" style="35" customWidth="1"/>
-    <col min="7" max="7" width="34" style="35" customWidth="1"/>
-    <col min="8" max="8" width="38" style="35" customWidth="1"/>
-    <col min="9" max="11" width="14" style="35" customWidth="1"/>
-    <col min="12" max="12" width="13" style="35" customWidth="1"/>
-    <col min="13" max="13" width="28" style="35" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="35"/>
+    <col min="1" max="1" width="13" style="28" customWidth="1"/>
+    <col min="2" max="2" width="28" style="28" customWidth="1"/>
+    <col min="3" max="3" width="16" style="28" customWidth="1"/>
+    <col min="4" max="4" width="10" style="28" customWidth="1"/>
+    <col min="5" max="5" width="38" style="28" customWidth="1"/>
+    <col min="6" max="6" width="30" style="28" customWidth="1"/>
+    <col min="7" max="7" width="34" style="28" customWidth="1"/>
+    <col min="8" max="8" width="38" style="28" customWidth="1"/>
+    <col min="9" max="11" width="14" style="28" customWidth="1"/>
+    <col min="12" max="12" width="13" style="28" customWidth="1"/>
+    <col min="13" max="13" width="28" style="28" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="A1" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="38" t="s">
+      <c r="A2" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="B2" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="C2" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="D2" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="F2" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="G2" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="H2" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="I2" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="M2" s="38" t="s">
-        <v>22</v>
+      <c r="J2" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="39" t="s">
+      <c r="A3" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="39" t="s">
+      <c r="D3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="F3" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="G3" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="H3" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
+      <c r="I3" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
     </row>
     <row r="4" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="39" t="s">
+      <c r="J4" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="K4" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
     </row>
     <row r="5" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A5" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="39" t="s">
+      <c r="A5" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="B5" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="D5" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="I5" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K5" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
+      <c r="F5" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
     </row>
     <row r="6" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A6" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="39" t="s">
+      <c r="A6" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="B6" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="D6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K6" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
+      <c r="F6" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
     </row>
     <row r="7" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="39" t="s">
+      <c r="A7" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="B7" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K7" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
+      <c r="F7" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
     </row>
     <row r="8" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A8" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="G8" s="39" t="s">
+      <c r="A8" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="B8" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="I8" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
+      <c r="F8" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
     </row>
     <row r="9" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A9" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="F9" s="39" t="s">
+      <c r="A9" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="B9" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="C9" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="I9" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K9" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
+      <c r="F9" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
     </row>
     <row r="10" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A10" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="G10" s="39" t="s">
+      <c r="A10" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="B10" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="I10" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J10" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K10" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
+      <c r="F10" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
     </row>
     <row r="11" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A11" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="F11" s="39" t="s">
+      <c r="A11" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="B11" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="D11" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="I11" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
+      <c r="F11" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
     </row>
     <row r="12" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
+      <c r="G12" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A13" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="G13" s="39" t="s">
+      <c r="A13" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="H13" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="H13" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K13" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
+      <c r="I13" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A14" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="G14" s="39" t="s">
+      <c r="A14" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="B14" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="I14" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K14" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
+      <c r="F14" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
     </row>
     <row r="15" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A15" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="G15" s="39" t="s">
+      <c r="A15" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="B15" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
+      <c r="F15" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
     </row>
     <row r="16" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A16" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="G16" s="39" t="s">
+      <c r="A16" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="B16" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
+      <c r="F16" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
     </row>
     <row r="17" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A17" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="F17" s="39" t="s">
+      <c r="A17" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="B17" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="C17" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
+      <c r="F17" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
     </row>
     <row r="18" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A18" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="G18" s="39" t="s">
+      <c r="A18" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="B18" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J18" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
+      <c r="F18" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
     </row>
     <row r="19" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A19" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="F19" s="39" t="s">
+      <c r="A19" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+    </row>
+    <row r="20" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A20" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+    </row>
+    <row r="21" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A21" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+    </row>
+    <row r="22" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A22" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+    </row>
+    <row r="23" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A23" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+    </row>
+    <row r="24" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A24" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+    </row>
+    <row r="25" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A25" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+    </row>
+    <row r="26" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A26" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+    </row>
+    <row r="27" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A27" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+    </row>
+    <row r="28" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A28" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K28" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+    </row>
+    <row r="29" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A29" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+    </row>
+    <row r="30" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A30" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J30" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K30" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+    </row>
+    <row r="31" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A31" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J31" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K31" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+    </row>
+    <row r="32" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A32" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J32" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+    </row>
+    <row r="33" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A33" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K33" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+    </row>
+    <row r="34" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A34" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J34" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K34" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+    </row>
+    <row r="35" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A35" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J35" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K35" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+    </row>
+    <row r="36" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A36" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J36" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K36" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+    </row>
+    <row r="37" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A37" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="H37" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J37" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K37" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+    </row>
+    <row r="38" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A38" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="H38" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J38" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K38" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+    </row>
+    <row r="39" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A39" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J39" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K39" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+    </row>
+    <row r="40" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A40" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="G40" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="I40" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J40" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+    </row>
+    <row r="41" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A41" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J41" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K41" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+    </row>
+    <row r="42" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A42" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="G42" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="H42" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J42" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K42" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+    </row>
+    <row r="43" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A43" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="G43" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J43" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K43" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+    </row>
+    <row r="44" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A44" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="G44" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="H44" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="G19" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J19" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-    </row>
-    <row r="20" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A20" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>254</v>
-      </c>
-      <c r="I20" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J20" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K20" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-    </row>
-    <row r="21" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A21" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>258</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J21" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-    </row>
-    <row r="22" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A22" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>262</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="I22" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J22" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K22" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="23" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A23" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I23" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J23" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K23" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-    </row>
-    <row r="24" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A24" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>271</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="I24" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K24" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-    </row>
-    <row r="25" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A25" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-    </row>
-    <row r="26" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A26" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>281</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="H26" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J26" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K26" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-    </row>
-    <row r="27" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A27" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J27" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K27" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-    </row>
-    <row r="28" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A28" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-    </row>
-    <row r="29" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A29" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>295</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>296</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J29" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K29" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-    </row>
-    <row r="30" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A30" s="39" t="s">
-        <v>299</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="G30" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-    </row>
-    <row r="31" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A31" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>307</v>
-      </c>
-      <c r="I31" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J31" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K31" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-    </row>
-    <row r="32" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A32" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="B32" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="G32" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="H32" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J32" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K32" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-    </row>
-    <row r="33" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A33" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J33" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K33" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-    </row>
-    <row r="34" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A34" s="39" t="s">
-        <v>318</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>319</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="G34" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="H34" s="39" t="s">
-        <v>322</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J34" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K34" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-    </row>
-    <row r="35" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A35" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="39" t="s">
+      <c r="I44" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J44" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K44" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+    </row>
+    <row r="45" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A45" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="G45" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="H45" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J45" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K45" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+    </row>
+    <row r="46" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A46" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="G46" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="H46" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J46" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K46" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+    </row>
+    <row r="47" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A47" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="I47" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J47" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K47" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+    </row>
+    <row r="48" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A48" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="H48" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="I48" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J48" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K48" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+    </row>
+    <row r="49" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A49" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>398</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J49" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+    </row>
+    <row r="50" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A50" s="32" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>404</v>
+      </c>
+      <c r="I50" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="F35" s="39" t="s">
-        <v>327</v>
-      </c>
-      <c r="G35" s="39" t="s">
-        <v>328</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>329</v>
-      </c>
-      <c r="I35" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J35" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K35" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-    </row>
-    <row r="36" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A36" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="G36" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="H36" s="39" t="s">
-        <v>334</v>
-      </c>
-      <c r="I36" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J36" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K36" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-    </row>
-    <row r="37" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A37" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="B37" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>336</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="I37" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J37" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K37" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-    </row>
-    <row r="38" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A38" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C38" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="39" t="s">
+      <c r="J50" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K50" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+    </row>
+    <row r="51" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A51" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>406</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>407</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>409</v>
+      </c>
+      <c r="I51" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J51" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K51" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+    </row>
+    <row r="52" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A52" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="F52" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>414</v>
+      </c>
+      <c r="I52" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J52" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K52" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+    </row>
+    <row r="53" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A53" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="G53" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="H53" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="I53" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J53" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K53" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+    </row>
+    <row r="54" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A54" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="F54" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="G54" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="H54" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J54" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K54" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+    </row>
+    <row r="55" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A55" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="32" t="s">
+        <v>428</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="G55" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="H55" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="I55" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J55" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K55" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+    </row>
+    <row r="56" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A56" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="G56" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="F38" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="G38" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="H38" s="39" t="s">
-        <v>343</v>
-      </c>
-      <c r="I38" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J38" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K38" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-    </row>
-    <row r="39" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A39" s="39" t="s">
-        <v>344</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>346</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="G39" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>349</v>
-      </c>
-      <c r="I39" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J39" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K39" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-    </row>
-    <row r="40" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A40" s="39" t="s">
-        <v>350</v>
-      </c>
-      <c r="B40" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C40" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="39" t="s">
-        <v>351</v>
-      </c>
-      <c r="F40" s="39" t="s">
-        <v>352</v>
-      </c>
-      <c r="G40" s="39" t="s">
-        <v>353</v>
-      </c>
-      <c r="H40" s="39" t="s">
-        <v>354</v>
-      </c>
-      <c r="I40" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J40" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K40" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-    </row>
-    <row r="41" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A41" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>356</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>357</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>358</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="I41" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J41" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K41" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-    </row>
-    <row r="42" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A42" s="39" t="s">
-        <v>360</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D42" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="39" t="s">
-        <v>362</v>
-      </c>
-      <c r="F42" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="G42" s="39" t="s">
-        <v>364</v>
-      </c>
-      <c r="H42" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="I42" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J42" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K42" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-    </row>
-    <row r="43" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A43" s="39" t="s">
-        <v>366</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D43" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="G43" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="I43" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J43" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K43" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-    </row>
-    <row r="44" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A44" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="D44" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>372</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="G44" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="H44" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="I44" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J44" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K44" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-    </row>
-    <row r="45" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A45" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>377</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="H45" s="39" t="s">
-        <v>379</v>
-      </c>
-      <c r="I45" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J45" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K45" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
-    </row>
-    <row r="46" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A46" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="G46" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="H46" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="I46" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J46" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K46" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L46" s="39"/>
-      <c r="M46" s="39"/>
-    </row>
-    <row r="47" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A47" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="G47" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="I47" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J47" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K47" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
-    </row>
-    <row r="48" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A48" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D48" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="G48" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="H48" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="I48" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J48" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K48" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
-    </row>
-    <row r="49" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A49" s="39" t="s">
-        <v>393</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C49" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>395</v>
-      </c>
-      <c r="G49" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="H49" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="I49" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="J49" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K49" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-    </row>
-    <row r="50" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A50" s="39" t="s">
-        <v>397</v>
-      </c>
-      <c r="B50" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C50" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="D50" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E50" s="39" t="s">
-        <v>399</v>
-      </c>
-      <c r="F50" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G50" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="H50" s="39" t="s">
-        <v>401</v>
-      </c>
-      <c r="I50" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J50" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K50" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
-    </row>
-    <row r="51" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A51" s="39" t="s">
-        <v>402</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C51" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="D51" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="39" t="s">
-        <v>403</v>
-      </c>
-      <c r="F51" s="39" t="s">
-        <v>404</v>
-      </c>
-      <c r="G51" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="H51" s="39" t="s">
-        <v>406</v>
-      </c>
-      <c r="I51" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J51" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K51" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L51" s="39"/>
-      <c r="M51" s="39"/>
-    </row>
-    <row r="52" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A52" s="39" t="s">
-        <v>407</v>
-      </c>
-      <c r="B52" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C52" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E52" s="39" t="s">
-        <v>408</v>
-      </c>
-      <c r="F52" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="G52" s="39" t="s">
-        <v>410</v>
-      </c>
-      <c r="H52" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I52" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J52" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K52" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-    </row>
-    <row r="53" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A53" s="39" t="s">
-        <v>412</v>
-      </c>
-      <c r="B53" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="C53" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D53" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E53" s="39" t="s">
-        <v>413</v>
-      </c>
-      <c r="F53" s="39" t="s">
-        <v>414</v>
-      </c>
-      <c r="G53" s="39" t="s">
-        <v>415</v>
-      </c>
-      <c r="H53" s="39" t="s">
-        <v>416</v>
-      </c>
-      <c r="I53" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J53" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K53" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-    </row>
-    <row r="54" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A54" s="39" t="s">
-        <v>417</v>
-      </c>
-      <c r="B54" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C54" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="D54" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="F54" s="39" t="s">
+      <c r="H56" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="I56" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J56" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K56" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+    </row>
+    <row r="57" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A57" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" s="32" t="s">
         <v>421</v>
       </c>
-      <c r="G54" s="39" t="s">
-        <v>422</v>
-      </c>
-      <c r="H54" s="39" t="s">
-        <v>423</v>
-      </c>
-      <c r="I54" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J54" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K54" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-    </row>
-    <row r="55" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A55" s="39" t="s">
-        <v>424</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C55" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>425</v>
-      </c>
-      <c r="F55" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="G55" s="39" t="s">
-        <v>427</v>
-      </c>
-      <c r="H55" s="39" t="s">
-        <v>428</v>
-      </c>
-      <c r="I55" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J55" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K55" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-    </row>
-    <row r="56" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A56" s="39" t="s">
-        <v>429</v>
-      </c>
-      <c r="B56" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C56" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="F56" s="39" t="s">
-        <v>431</v>
-      </c>
-      <c r="G56" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="H56" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="I56" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="J56" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K56" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-    </row>
-    <row r="57" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A57" s="39" t="s">
-        <v>433</v>
-      </c>
-      <c r="B57" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C57" s="39" t="s">
-        <v>434</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" s="39" t="s">
-        <v>435</v>
-      </c>
-      <c r="F57" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="G57" s="39" t="s">
+      <c r="C57" s="32" t="s">
         <v>437</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="D57" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E57" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="I57" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J57" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K57" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L57" s="39"/>
-      <c r="M57" s="39"/>
+      <c r="F57" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="G57" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="H57" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="J57" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K57" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
     </row>
     <row r="58" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A58" s="39" t="s">
-        <v>439</v>
-      </c>
-      <c r="B58" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C58" s="39" t="s">
-        <v>434</v>
-      </c>
-      <c r="D58" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="39" t="s">
-        <v>440</v>
-      </c>
-      <c r="F58" s="39" t="s">
-        <v>441</v>
-      </c>
-      <c r="G58" s="39" t="s">
+      <c r="A58" s="32" t="s">
         <v>442</v>
       </c>
-      <c r="H58" s="39" t="s">
+      <c r="B58" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="32" t="s">
         <v>443</v>
       </c>
-      <c r="I58" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J58" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K58" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L58" s="39"/>
-      <c r="M58" s="39"/>
+      <c r="F58" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="G58" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="H58" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="I58" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K58" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
     </row>
     <row r="59" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A59" s="39" t="s">
-        <v>444</v>
-      </c>
-      <c r="B59" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="C59" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="39" t="s">
-        <v>446</v>
-      </c>
-      <c r="F59" s="39" t="s">
+      <c r="A59" s="32" t="s">
         <v>447</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="B59" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="C59" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="H59" s="39" t="s">
+      <c r="D59" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E59" s="32" t="s">
         <v>449</v>
       </c>
-      <c r="I59" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J59" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="K59" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
+      <c r="F59" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="G59" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="H59" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="I59" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="J59" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="K59" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
     </row>
     <row r="60" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A60" s="36"/>
+      <c r="A60" s="29"/>
     </row>
     <row r="61" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A61" s="36"/>
+      <c r="A61" s="29"/>
     </row>
     <row r="62" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A62" s="36"/>
+      <c r="A62" s="29"/>
     </row>
     <row r="63" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A63" s="36"/>
+      <c r="A63" s="29"/>
     </row>
     <row r="64" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A64" s="36"/>
+      <c r="A64" s="29"/>
     </row>
     <row r="65" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A65" s="36"/>
+      <c r="A65" s="29"/>
     </row>
     <row r="66" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A66" s="36"/>
+      <c r="A66" s="29"/>
     </row>
     <row r="67" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A67" s="36"/>
+      <c r="A67" s="29"/>
     </row>
     <row r="68" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A68" s="36"/>
+      <c r="A68" s="29"/>
     </row>
     <row r="69" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A69" s="36"/>
+      <c r="A69" s="29"/>
     </row>
     <row r="70" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A70" s="36"/>
+      <c r="A70" s="29"/>
     </row>
     <row r="71" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A71" s="36"/>
+      <c r="A71" s="29"/>
     </row>
     <row r="72" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A72" s="36"/>
+      <c r="A72" s="29"/>
     </row>
     <row r="73" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A73" s="36"/>
+      <c r="A73" s="29"/>
     </row>
     <row r="74" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A74" s="36"/>
+      <c r="A74" s="29"/>
     </row>
     <row r="75" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A75" s="36"/>
+      <c r="A75" s="29"/>
     </row>
     <row r="76" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A76" s="36"/>
+      <c r="A76" s="29"/>
     </row>
     <row r="77" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A77" s="36"/>
+      <c r="A77" s="29"/>
     </row>
     <row r="78" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A78" s="36"/>
+      <c r="A78" s="29"/>
     </row>
     <row r="79" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A79" s="36"/>
+      <c r="A79" s="29"/>
     </row>
     <row r="80" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A80" s="36"/>
+      <c r="A80" s="29"/>
     </row>
     <row r="81" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A81" s="36"/>
+      <c r="A81" s="29"/>
     </row>
     <row r="82" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A82" s="36"/>
+      <c r="A82" s="29"/>
     </row>
     <row r="83" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A83" s="36"/>
+      <c r="A83" s="29"/>
     </row>
     <row r="84" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A84" s="36"/>
+      <c r="A84" s="29"/>
     </row>
     <row r="85" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A85" s="36"/>
+      <c r="A85" s="29"/>
     </row>
     <row r="86" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A86" s="36"/>
+      <c r="A86" s="29"/>
     </row>
     <row r="87" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A87" s="36"/>
+      <c r="A87" s="29"/>
     </row>
     <row r="88" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A88" s="36"/>
+      <c r="A88" s="29"/>
     </row>
     <row r="89" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A89" s="36"/>
+      <c r="A89" s="29"/>
     </row>
     <row r="90" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A90" s="36"/>
+      <c r="A90" s="29"/>
     </row>
     <row r="91" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A91" s="36"/>
+      <c r="A91" s="29"/>
     </row>
     <row r="92" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A92" s="36"/>
+      <c r="A92" s="29"/>
     </row>
     <row r="93" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A93" s="36"/>
+      <c r="A93" s="29"/>
     </row>
     <row r="94" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A94" s="36"/>
+      <c r="A94" s="29"/>
     </row>
     <row r="95" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A95" s="36"/>
+      <c r="A95" s="29"/>
     </row>
     <row r="96" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A96" s="36"/>
+      <c r="A96" s="29"/>
     </row>
     <row r="97" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A97" s="36"/>
+      <c r="A97" s="29"/>
     </row>
     <row r="98" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A98" s="36"/>
+      <c r="A98" s="29"/>
     </row>
     <row r="99" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A99" s="36"/>
+      <c r="A99" s="29"/>
     </row>
     <row r="100" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A100" s="36"/>
+      <c r="A100" s="29"/>
     </row>
     <row r="101" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A101" s="36"/>
+      <c r="A101" s="29"/>
     </row>
     <row r="102" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A102" s="36"/>
+      <c r="A102" s="29"/>
     </row>
     <row r="103" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A103" s="36"/>
+      <c r="A103" s="29"/>
     </row>
     <row r="104" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A104" s="36"/>
+      <c r="A104" s="29"/>
     </row>
     <row r="105" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A105" s="36"/>
+      <c r="A105" s="29"/>
     </row>
     <row r="106" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A106" s="36"/>
+      <c r="A106" s="29"/>
     </row>
     <row r="107" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A107" s="36"/>
+      <c r="A107" s="29"/>
     </row>
     <row r="108" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A108" s="36"/>
+      <c r="A108" s="29"/>
     </row>
     <row r="109" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A109" s="36"/>
+      <c r="A109" s="29"/>
     </row>
     <row r="110" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A110" s="36"/>
+      <c r="A110" s="29"/>
     </row>
     <row r="111" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A111" s="36"/>
+      <c r="A111" s="29"/>
     </row>
     <row r="112" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A112" s="36"/>
+      <c r="A112" s="29"/>
     </row>
     <row r="113" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A113" s="36"/>
+      <c r="A113" s="29"/>
     </row>
     <row r="114" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A114" s="36"/>
+      <c r="A114" s="29"/>
     </row>
     <row r="115" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A115" s="36"/>
+      <c r="A115" s="29"/>
     </row>
     <row r="116" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A116" s="36"/>
+      <c r="A116" s="29"/>
     </row>
     <row r="117" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A117" s="36"/>
+      <c r="A117" s="29"/>
     </row>
     <row r="118" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A118" s="36"/>
+      <c r="A118" s="29"/>
     </row>
     <row r="119" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A119" s="36"/>
+      <c r="A119" s="29"/>
     </row>
     <row r="120" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A120" s="36"/>
+      <c r="A120" s="29"/>
     </row>
     <row r="121" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A121" s="36"/>
+      <c r="A121" s="29"/>
     </row>
     <row r="122" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A122" s="36"/>
+      <c r="A122" s="29"/>
     </row>
     <row r="123" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A123" s="36"/>
+      <c r="A123" s="29"/>
     </row>
     <row r="124" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A124" s="36"/>
+      <c r="A124" s="29"/>
     </row>
     <row r="125" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A125" s="36"/>
+      <c r="A125" s="29"/>
     </row>
     <row r="126" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A126" s="36"/>
+      <c r="A126" s="29"/>
     </row>
     <row r="127" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A127" s="36"/>
+      <c r="A127" s="29"/>
     </row>
     <row r="128" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A128" s="36"/>
+      <c r="A128" s="29"/>
     </row>
     <row r="129" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A129" s="36"/>
+      <c r="A129" s="29"/>
     </row>
     <row r="130" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A130" s="36"/>
+      <c r="A130" s="29"/>
     </row>
     <row r="131" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A131" s="36"/>
+      <c r="A131" s="29"/>
     </row>
     <row r="132" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A132" s="36"/>
+      <c r="A132" s="29"/>
     </row>
     <row r="133" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A133" s="36"/>
+      <c r="A133" s="29"/>
     </row>
     <row r="134" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A134" s="36"/>
+      <c r="A134" s="29"/>
     </row>
     <row r="135" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A135" s="36"/>
+      <c r="A135" s="29"/>
     </row>
     <row r="136" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A136" s="36"/>
+      <c r="A136" s="29"/>
     </row>
     <row r="137" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A137" s="36"/>
+      <c r="A137" s="29"/>
     </row>
     <row r="138" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A138" s="36"/>
+      <c r="A138" s="29"/>
     </row>
     <row r="139" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A139" s="36"/>
+      <c r="A139" s="29"/>
     </row>
     <row r="140" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A140" s="36"/>
+      <c r="A140" s="29"/>
     </row>
     <row r="141" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A141" s="36"/>
+      <c r="A141" s="29"/>
     </row>
     <row r="142" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A142" s="36"/>
+      <c r="A142" s="29"/>
     </row>
     <row r="143" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A143" s="36"/>
+      <c r="A143" s="29"/>
     </row>
     <row r="144" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A144" s="36"/>
+      <c r="A144" s="29"/>
     </row>
     <row r="145" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A145" s="36"/>
+      <c r="A145" s="29"/>
     </row>
     <row r="146" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A146" s="36"/>
+      <c r="A146" s="29"/>
     </row>
     <row r="147" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A147" s="36"/>
+      <c r="A147" s="29"/>
     </row>
     <row r="148" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A148" s="36"/>
+      <c r="A148" s="29"/>
     </row>
     <row r="149" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A149" s="36"/>
+      <c r="A149" s="29"/>
     </row>
     <row r="150" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A150" s="36"/>
+      <c r="A150" s="29"/>
     </row>
     <row r="151" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A151" s="36"/>
+      <c r="A151" s="29"/>
     </row>
     <row r="152" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A152" s="36"/>
+      <c r="A152" s="29"/>
     </row>
     <row r="153" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A153" s="36"/>
+      <c r="A153" s="29"/>
     </row>
     <row r="154" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A154" s="36"/>
+      <c r="A154" s="29"/>
     </row>
     <row r="155" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A155" s="36"/>
+      <c r="A155" s="29"/>
     </row>
     <row r="156" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A156" s="36"/>
+      <c r="A156" s="29"/>
     </row>
     <row r="157" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A157" s="36"/>
+      <c r="A157" s="29"/>
     </row>
     <row r="158" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A158" s="36"/>
+      <c r="A158" s="29"/>
     </row>
     <row r="159" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A159" s="36"/>
+      <c r="A159" s="29"/>
     </row>
     <row r="160" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A160" s="36"/>
+      <c r="A160" s="29"/>
     </row>
     <row r="161" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A161" s="36"/>
+      <c r="A161" s="29"/>
     </row>
     <row r="162" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A162" s="36"/>
+      <c r="A162" s="29"/>
     </row>
     <row r="163" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A163" s="36"/>
+      <c r="A163" s="29"/>
     </row>
     <row r="164" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A164" s="36"/>
+      <c r="A164" s="29"/>
     </row>
     <row r="165" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A165" s="36"/>
+      <c r="A165" s="29"/>
     </row>
     <row r="166" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A166" s="36"/>
+      <c r="A166" s="29"/>
     </row>
     <row r="167" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A167" s="36"/>
+      <c r="A167" s="29"/>
     </row>
     <row r="168" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A168" s="36"/>
+      <c r="A168" s="29"/>
     </row>
     <row r="169" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A169" s="36"/>
+      <c r="A169" s="29"/>
     </row>
     <row r="170" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A170" s="36"/>
+      <c r="A170" s="29"/>
     </row>
     <row r="171" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A171" s="36"/>
+      <c r="A171" s="29"/>
     </row>
     <row r="172" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A172" s="36"/>
+      <c r="A172" s="29"/>
     </row>
     <row r="173" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A173" s="36"/>
+      <c r="A173" s="29"/>
     </row>
     <row r="174" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A174" s="36"/>
+      <c r="A174" s="29"/>
     </row>
     <row r="175" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A175" s="36"/>
+      <c r="A175" s="29"/>
     </row>
     <row r="176" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A176" s="36"/>
+      <c r="A176" s="29"/>
     </row>
     <row r="177" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A177" s="36"/>
+      <c r="A177" s="29"/>
     </row>
     <row r="178" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A178" s="36"/>
+      <c r="A178" s="29"/>
     </row>
     <row r="179" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A179" s="36"/>
+      <c r="A179" s="29"/>
     </row>
     <row r="180" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A180" s="36"/>
+      <c r="A180" s="29"/>
     </row>
     <row r="181" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A181" s="36"/>
+      <c r="A181" s="29"/>
     </row>
     <row r="182" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A182" s="36"/>
+      <c r="A182" s="29"/>
     </row>
     <row r="183" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A183" s="36"/>
+      <c r="A183" s="29"/>
     </row>
     <row r="184" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A184" s="36"/>
+      <c r="A184" s="29"/>
     </row>
     <row r="185" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A185" s="36"/>
+      <c r="A185" s="29"/>
     </row>
     <row r="186" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A186" s="36"/>
+      <c r="A186" s="29"/>
     </row>
     <row r="187" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A187" s="36"/>
+      <c r="A187" s="29"/>
     </row>
     <row r="188" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A188" s="36"/>
+      <c r="A188" s="29"/>
     </row>
     <row r="189" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A189" s="36"/>
+      <c r="A189" s="29"/>
     </row>
     <row r="190" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A190" s="36"/>
+      <c r="A190" s="29"/>
     </row>
     <row r="191" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A191" s="36"/>
+      <c r="A191" s="29"/>
     </row>
     <row r="192" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A192" s="36"/>
+      <c r="A192" s="29"/>
     </row>
     <row r="193" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A193" s="36"/>
+      <c r="A193" s="29"/>
     </row>
     <row r="194" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A194" s="36"/>
+      <c r="A194" s="29"/>
     </row>
     <row r="195" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A195" s="36"/>
+      <c r="A195" s="29"/>
     </row>
     <row r="196" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A196" s="36"/>
+      <c r="A196" s="29"/>
     </row>
     <row r="197" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A197" s="36"/>
+      <c r="A197" s="29"/>
     </row>
     <row r="198" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A198" s="36"/>
+      <c r="A198" s="29"/>
     </row>
     <row r="199" spans="1:1" ht="38.1" customHeight="1">
-      <c r="A199" s="36"/>
+      <c r="A199" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Plan.xlsx
+++ b/Plan.xlsx
@@ -3294,11 +3294,10 @@
         <v>35</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" ref="I5" si="0">IF(H5="Done",100,IF(H5="In Progress",50,IF(H5="Blocked",25,0)))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>37</v>
@@ -3331,11 +3330,10 @@
         <v>42</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" ref="I6:I23" si="1">IF(H6="Done",100,IF(H6="In Progress",50,IF(H6="Blocked",25,0)))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>44</v>
@@ -3368,11 +3366,10 @@
         <v>49</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>50</v>
@@ -3405,11 +3402,10 @@
         <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>56</v>
@@ -3442,11 +3438,10 @@
         <v>55</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>61</v>
@@ -3479,11 +3474,10 @@
         <v>66</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>67</v>
@@ -3516,11 +3510,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>73</v>
@@ -3553,11 +3546,10 @@
         <v>78</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>79</v>
@@ -3590,11 +3582,10 @@
         <v>84</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>85</v>
@@ -3627,11 +3618,10 @@
         <v>90</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I14" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>91</v>
@@ -3664,11 +3654,10 @@
         <v>96</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>97</v>
@@ -3701,11 +3690,10 @@
         <v>102</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>103</v>
@@ -3738,11 +3726,10 @@
         <v>109</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>110</v>
@@ -3775,11 +3762,10 @@
         <v>115</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>116</v>
@@ -3812,11 +3798,10 @@
         <v>121</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I19" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>122</v>
@@ -3849,11 +3834,10 @@
         <v>128</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>129</v>
@@ -3886,11 +3870,10 @@
         <v>134</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>135</v>
@@ -3923,11 +3906,10 @@
         <v>140</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>141</v>
@@ -3963,7 +3945,6 @@
         <v>43</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="7" t="s">

--- a/Plan.xlsx
+++ b/Plan.xlsx
@@ -3654,10 +3654,12 @@
         <v>96</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="6">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="J15" s="4" t="s">
         <v>97</v>
@@ -4217,14 +4219,20 @@
       <c r="I3" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J3" s="32" t="s">
-        <v>169</v>
+      <c r="J3" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K3" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
+      <c r="M3" s="32" t="inlineStr">
+        <is>
+          <t>test_auth_flow.py</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="38.1" customHeight="1">
       <c r="A4" s="32" t="s">
@@ -4254,14 +4262,20 @@
       <c r="I4" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J4" s="32" t="s">
-        <v>169</v>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K4" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
+      <c r="M4" s="32" t="inlineStr">
+        <is>
+          <t>test_auth_flow.py</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="38.1" customHeight="1">
       <c r="A5" s="32" t="s">
@@ -4291,14 +4305,20 @@
       <c r="I5" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>169</v>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K5" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
+      <c r="M5" s="32" t="inlineStr">
+        <is>
+          <t>test_auth_flow.py</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="38.1" customHeight="1">
       <c r="A6" s="32" t="s">
@@ -4328,14 +4348,20 @@
       <c r="I6" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>169</v>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K6" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
+      <c r="M6" s="32" t="inlineStr">
+        <is>
+          <t>test_products.py / test_vouchers.py</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="38.1" customHeight="1">
       <c r="A7" s="32" t="s">
@@ -4365,14 +4391,20 @@
       <c r="I7" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J7" s="32" t="s">
-        <v>169</v>
+      <c r="J7" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K7" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
+      <c r="M7" s="32" t="inlineStr">
+        <is>
+          <t>test_shops.py / test_fulfilment.py</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="38.1" customHeight="1">
       <c r="A8" s="32" t="s">
@@ -4439,14 +4471,20 @@
       <c r="I9" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J9" s="32" t="s">
-        <v>169</v>
+      <c r="J9" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K9" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>test_shops.py</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="38.1" customHeight="1">
       <c r="A10" s="32" t="s">
@@ -4476,14 +4514,20 @@
       <c r="I10" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J10" s="32" t="s">
-        <v>169</v>
+      <c r="J10" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K10" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
+      <c r="M10" s="32" t="inlineStr">
+        <is>
+          <t>test_shops.py</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="38.1" customHeight="1">
       <c r="A11" s="32" t="s">
@@ -4513,14 +4557,20 @@
       <c r="I11" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J11" s="32" t="s">
-        <v>169</v>
+      <c r="J11" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K11" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>test_products.py</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="38.1" customHeight="1">
       <c r="A12" s="32" t="s">
@@ -4550,14 +4600,20 @@
       <c r="I12" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J12" s="32" t="s">
-        <v>169</v>
+      <c r="J12" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K12" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="M12" s="32" t="inlineStr">
+        <is>
+          <t>test_products.py</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="38.1" customHeight="1">
       <c r="A13" s="32" t="s">
@@ -4587,14 +4643,20 @@
       <c r="I13" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J13" s="32" t="s">
-        <v>169</v>
+      <c r="J13" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K13" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>test_products.py</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="38.1" customHeight="1">
       <c r="A14" s="32" t="s">
@@ -4735,14 +4797,20 @@
       <c r="I17" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J17" s="32" t="s">
-        <v>169</v>
+      <c r="J17" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K17" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="38.1" customHeight="1">
       <c r="A18" s="32" t="s">
@@ -4772,14 +4840,20 @@
       <c r="I18" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J18" s="32" t="s">
-        <v>169</v>
+      <c r="J18" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K18" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="M18" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="38.1" customHeight="1">
       <c r="A19" s="32" t="s">
@@ -4809,14 +4883,20 @@
       <c r="I19" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J19" s="32" t="s">
-        <v>169</v>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K19" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="38.1" customHeight="1">
       <c r="A20" s="32" t="s">
@@ -4846,14 +4926,20 @@
       <c r="I20" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J20" s="32" t="s">
-        <v>169</v>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K20" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
+      <c r="M20" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="38.1" customHeight="1">
       <c r="A21" s="32" t="s">
@@ -4883,14 +4969,20 @@
       <c r="I21" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J21" s="32" t="s">
-        <v>169</v>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K21" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
+      <c r="M21" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="38.1" customHeight="1">
       <c r="A22" s="32" t="s">
@@ -4957,14 +5049,20 @@
       <c r="I23" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J23" s="32" t="s">
-        <v>169</v>
+      <c r="J23" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K23" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="M23" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="1:13" ht="38.1" customHeight="1">
       <c r="A24" s="32" t="s">
@@ -4994,14 +5092,20 @@
       <c r="I24" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J24" s="32" t="s">
-        <v>169</v>
+      <c r="J24" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K24" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="38.1" customHeight="1">
       <c r="A25" s="32" t="s">
@@ -5031,14 +5135,20 @@
       <c r="I25" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="32" t="s">
-        <v>169</v>
+      <c r="J25" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K25" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="M25" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:13" ht="38.1" customHeight="1">
       <c r="A26" s="32" t="s">
@@ -5068,14 +5178,20 @@
       <c r="I26" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J26" s="32" t="s">
-        <v>169</v>
+      <c r="J26" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K26" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:13" ht="38.1" customHeight="1">
       <c r="A27" s="32" t="s">
@@ -5105,14 +5221,20 @@
       <c r="I27" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J27" s="32" t="s">
-        <v>169</v>
+      <c r="J27" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K27" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
+      <c r="M27" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:13" ht="38.1" customHeight="1">
       <c r="A28" s="32" t="s">
@@ -5142,14 +5264,20 @@
       <c r="I28" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J28" s="32" t="s">
-        <v>169</v>
+      <c r="J28" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K28" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="38.1" customHeight="1">
       <c r="A29" s="32" t="s">
@@ -5179,14 +5307,20 @@
       <c r="I29" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="32" t="s">
-        <v>169</v>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K29" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="38.1" customHeight="1">
       <c r="A30" s="32" t="s">
@@ -5216,14 +5350,20 @@
       <c r="I30" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J30" s="32" t="s">
-        <v>169</v>
+      <c r="J30" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K30" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
+      <c r="M30" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:13" ht="38.1" customHeight="1">
       <c r="A31" s="32" t="s">
@@ -5253,14 +5393,20 @@
       <c r="I31" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J31" s="32" t="s">
-        <v>169</v>
+      <c r="J31" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K31" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:13" ht="38.1" customHeight="1">
       <c r="A32" s="32" t="s">
@@ -5290,14 +5436,20 @@
       <c r="I32" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J32" s="32" t="s">
-        <v>169</v>
+      <c r="J32" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K32" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
+      <c r="M32" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:13" ht="38.1" customHeight="1">
       <c r="A33" s="32" t="s">
@@ -5327,14 +5479,20 @@
       <c r="I33" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J33" s="32" t="s">
-        <v>169</v>
+      <c r="J33" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K33" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="M33" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="38.1" customHeight="1">
       <c r="A34" s="32" t="s">
@@ -5401,14 +5559,20 @@
       <c r="I35" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J35" s="32" t="s">
-        <v>169</v>
+      <c r="J35" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K35" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
+      <c r="M35" s="32" t="inlineStr">
+        <is>
+          <t>test_inventory_hold.py</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="38.1" customHeight="1">
       <c r="A36" s="32" t="s">
@@ -5475,14 +5639,20 @@
       <c r="I37" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J37" s="32" t="s">
-        <v>169</v>
+      <c r="J37" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K37" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
+      <c r="M37" s="32" t="inlineStr">
+        <is>
+          <t>test_inventory_hold.py</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="38.1" customHeight="1">
       <c r="A38" s="32" t="s">
@@ -5512,14 +5682,20 @@
       <c r="I38" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J38" s="32" t="s">
-        <v>169</v>
+      <c r="J38" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K38" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
+      <c r="M38" s="32" t="inlineStr">
+        <is>
+          <t>test_inventory_hold.py</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:13" ht="38.1" customHeight="1">
       <c r="A39" s="32" t="s">
@@ -5549,14 +5725,20 @@
       <c r="I39" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J39" s="32" t="s">
-        <v>169</v>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K39" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
+      <c r="M39" s="32" t="inlineStr">
+        <is>
+          <t>test_orders.py / test_variants.py</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="38.1" customHeight="1">
       <c r="A40" s="32" t="s">
@@ -5660,14 +5842,20 @@
       <c r="I42" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J42" s="32" t="s">
-        <v>169</v>
+      <c r="J42" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K42" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
+      <c r="M42" s="32" t="inlineStr">
+        <is>
+          <t>test_payments.py</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:13" ht="38.1" customHeight="1">
       <c r="A43" s="32" t="s">
@@ -5697,14 +5885,20 @@
       <c r="I43" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J43" s="32" t="s">
-        <v>169</v>
+      <c r="J43" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K43" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
+      <c r="M43" s="32" t="inlineStr">
+        <is>
+          <t>test_fulfilment.py</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="1:13" ht="38.1" customHeight="1">
       <c r="A44" s="32" t="s">
@@ -5734,14 +5928,20 @@
       <c r="I44" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J44" s="32" t="s">
-        <v>169</v>
+      <c r="J44" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K44" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
+      <c r="M44" s="32" t="inlineStr">
+        <is>
+          <t>test_fulfilment.py</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="1:13" ht="38.1" customHeight="1">
       <c r="A45" s="32" t="s">
@@ -5882,14 +6082,20 @@
       <c r="I48" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J48" s="32" t="s">
-        <v>169</v>
+      <c r="J48" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K48" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
+      <c r="M48" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:13" ht="38.1" customHeight="1">
       <c r="A49" s="32" t="s">
@@ -5919,14 +6125,20 @@
       <c r="I49" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="J49" s="32" t="s">
-        <v>169</v>
+      <c r="J49" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K49" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_orders.py</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:13" ht="38.1" customHeight="1">
       <c r="A50" s="32" t="s">
@@ -6067,14 +6279,20 @@
       <c r="I53" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="J53" s="32" t="s">
-        <v>169</v>
+      <c r="J53" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K53" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L53" s="32"/>
-      <c r="M53" s="32"/>
+      <c r="M53" s="32" t="inlineStr">
+        <is>
+          <t>test_uploads.py</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:13" ht="38.1" customHeight="1">
       <c r="A54" s="32" t="s">

--- a/Plan.xlsx
+++ b/Plan.xlsx
@@ -4216,8 +4216,10 @@
       <c r="H3" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="I3" s="32" t="s">
-        <v>168</v>
+      <c r="I3" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J3" s="32" t="inlineStr">
         <is>
@@ -4259,8 +4261,10 @@
       <c r="H4" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>168</v>
+      <c r="I4" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J4" s="32" t="inlineStr">
         <is>
@@ -4302,8 +4306,10 @@
       <c r="H5" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="I5" s="32" t="s">
-        <v>168</v>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J5" s="32" t="inlineStr">
         <is>
@@ -4345,8 +4351,10 @@
       <c r="H6" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>168</v>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
@@ -4388,8 +4396,10 @@
       <c r="H7" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="32" t="s">
-        <v>168</v>
+      <c r="I7" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J7" s="32" t="inlineStr">
         <is>
@@ -4431,17 +4441,25 @@
       <c r="H8" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="I8" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>169</v>
+      <c r="I8" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K8" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
+      <c r="M8" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="38.1" customHeight="1">
       <c r="A9" s="32" t="s">
@@ -4468,8 +4486,10 @@
       <c r="H9" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="I9" s="32" t="s">
-        <v>168</v>
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J9" s="32" t="inlineStr">
         <is>
@@ -4511,8 +4531,10 @@
       <c r="H10" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="I10" s="32" t="s">
-        <v>168</v>
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J10" s="32" t="inlineStr">
         <is>
@@ -4554,8 +4576,10 @@
       <c r="H11" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="I11" s="32" t="s">
-        <v>168</v>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J11" s="32" t="inlineStr">
         <is>
@@ -4597,8 +4621,10 @@
       <c r="H12" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="I12" s="32" t="s">
-        <v>168</v>
+      <c r="I12" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J12" s="32" t="inlineStr">
         <is>
@@ -4640,8 +4666,10 @@
       <c r="H13" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>168</v>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J13" s="32" t="inlineStr">
         <is>
@@ -4683,17 +4711,25 @@
       <c r="H14" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="I14" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>169</v>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K14" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="38.1" customHeight="1">
       <c r="A15" s="32" t="s">
@@ -4720,17 +4756,25 @@
       <c r="H15" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="I15" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>169</v>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K15" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="38.1" customHeight="1">
       <c r="A16" s="32" t="s">
@@ -4757,17 +4801,25 @@
       <c r="H16" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="I16" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>169</v>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K16" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="38.1" customHeight="1">
       <c r="A17" s="32" t="s">
@@ -4794,8 +4846,10 @@
       <c r="H17" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="I17" s="32" t="s">
-        <v>168</v>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J17" s="32" t="inlineStr">
         <is>
@@ -4837,8 +4891,10 @@
       <c r="H18" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="I18" s="32" t="s">
-        <v>168</v>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J18" s="32" t="inlineStr">
         <is>
@@ -4880,8 +4936,10 @@
       <c r="H19" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="I19" s="32" t="s">
-        <v>168</v>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J19" s="32" t="inlineStr">
         <is>
@@ -4923,8 +4981,10 @@
       <c r="H20" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="I20" s="32" t="s">
-        <v>168</v>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J20" s="32" t="inlineStr">
         <is>
@@ -4966,8 +5026,10 @@
       <c r="H21" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="I21" s="32" t="s">
-        <v>168</v>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J21" s="32" t="inlineStr">
         <is>
@@ -5009,17 +5071,25 @@
       <c r="H22" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="I22" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>169</v>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K22" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+      <c r="M22" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:13" ht="38.1" customHeight="1">
       <c r="A23" s="32" t="s">
@@ -5046,8 +5116,10 @@
       <c r="H23" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="I23" s="32" t="s">
-        <v>168</v>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J23" s="32" t="inlineStr">
         <is>
@@ -5089,8 +5161,10 @@
       <c r="H24" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="I24" s="32" t="s">
-        <v>168</v>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J24" s="32" t="inlineStr">
         <is>
@@ -5132,8 +5206,10 @@
       <c r="H25" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="I25" s="32" t="s">
-        <v>168</v>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J25" s="32" t="inlineStr">
         <is>
@@ -5175,8 +5251,10 @@
       <c r="H26" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="I26" s="32" t="s">
-        <v>168</v>
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J26" s="32" t="inlineStr">
         <is>
@@ -5218,8 +5296,10 @@
       <c r="H27" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="I27" s="32" t="s">
-        <v>168</v>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J27" s="32" t="inlineStr">
         <is>
@@ -5261,8 +5341,10 @@
       <c r="H28" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="I28" s="32" t="s">
-        <v>168</v>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J28" s="32" t="inlineStr">
         <is>
@@ -5304,8 +5386,10 @@
       <c r="H29" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="I29" s="32" t="s">
-        <v>168</v>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J29" s="32" t="inlineStr">
         <is>
@@ -5347,8 +5431,10 @@
       <c r="H30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="I30" s="32" t="s">
-        <v>168</v>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J30" s="32" t="inlineStr">
         <is>
@@ -5390,8 +5476,10 @@
       <c r="H31" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="I31" s="32" t="s">
-        <v>168</v>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J31" s="32" t="inlineStr">
         <is>
@@ -5433,8 +5521,10 @@
       <c r="H32" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="I32" s="32" t="s">
-        <v>168</v>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J32" s="32" t="inlineStr">
         <is>
@@ -5476,8 +5566,10 @@
       <c r="H33" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="I33" s="32" t="s">
-        <v>168</v>
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J33" s="32" t="inlineStr">
         <is>
@@ -5519,17 +5611,25 @@
       <c r="H34" s="32" t="s">
         <v>325</v>
       </c>
-      <c r="I34" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J34" s="32" t="s">
-        <v>169</v>
+      <c r="I34" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K34" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
+      <c r="M34" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="38.1" customHeight="1">
       <c r="A35" s="32" t="s">
@@ -5556,8 +5656,10 @@
       <c r="H35" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="I35" s="32" t="s">
-        <v>168</v>
+      <c r="I35" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J35" s="32" t="inlineStr">
         <is>
@@ -5599,17 +5701,25 @@
       <c r="H36" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="I36" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J36" s="32" t="s">
-        <v>169</v>
+      <c r="I36" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K36" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
+      <c r="M36" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="38.1" customHeight="1">
       <c r="A37" s="32" t="s">
@@ -5636,8 +5746,10 @@
       <c r="H37" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="I37" s="32" t="s">
-        <v>168</v>
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J37" s="32" t="inlineStr">
         <is>
@@ -5679,8 +5791,10 @@
       <c r="H38" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="I38" s="32" t="s">
-        <v>168</v>
+      <c r="I38" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J38" s="32" t="inlineStr">
         <is>
@@ -5722,8 +5836,10 @@
       <c r="H39" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="I39" s="32" t="s">
-        <v>168</v>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J39" s="32" t="inlineStr">
         <is>
@@ -5765,17 +5881,25 @@
       <c r="H40" s="32" t="s">
         <v>357</v>
       </c>
-      <c r="I40" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J40" s="32" t="s">
-        <v>169</v>
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K40" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
+      <c r="M40" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="38.1" customHeight="1">
       <c r="A41" s="32" t="s">
@@ -5802,17 +5926,25 @@
       <c r="H41" s="32" t="s">
         <v>362</v>
       </c>
-      <c r="I41" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J41" s="32" t="s">
-        <v>169</v>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K41" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
+      <c r="M41" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="38.1" customHeight="1">
       <c r="A42" s="32" t="s">
@@ -5839,8 +5971,10 @@
       <c r="H42" s="32" t="s">
         <v>368</v>
       </c>
-      <c r="I42" s="32" t="s">
-        <v>168</v>
+      <c r="I42" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J42" s="32" t="inlineStr">
         <is>
@@ -5882,8 +6016,10 @@
       <c r="H43" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="I43" s="32" t="s">
-        <v>168</v>
+      <c r="I43" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J43" s="32" t="inlineStr">
         <is>
@@ -5925,8 +6061,10 @@
       <c r="H44" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="I44" s="32" t="s">
-        <v>168</v>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J44" s="32" t="inlineStr">
         <is>
@@ -5968,17 +6106,25 @@
       <c r="H45" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="I45" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J45" s="32" t="s">
-        <v>169</v>
+      <c r="I45" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K45" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="38.1" customHeight="1">
       <c r="A46" s="32" t="s">
@@ -6005,17 +6151,25 @@
       <c r="H46" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="I46" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J46" s="32" t="s">
-        <v>169</v>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K46" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
+      <c r="M46" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="38.1" customHeight="1">
       <c r="A47" s="32" t="s">
@@ -6042,17 +6196,25 @@
       <c r="H47" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="I47" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J47" s="32" t="s">
-        <v>169</v>
+      <c r="I47" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K47" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="38.1" customHeight="1">
       <c r="A48" s="32" t="s">
@@ -6079,8 +6241,10 @@
       <c r="H48" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="I48" s="32" t="s">
-        <v>168</v>
+      <c r="I48" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J48" s="32" t="inlineStr">
         <is>
@@ -6122,8 +6286,10 @@
       <c r="H49" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="I49" s="32" t="s">
-        <v>168</v>
+      <c r="I49" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J49" s="32" t="inlineStr">
         <is>
@@ -6165,17 +6331,25 @@
       <c r="H50" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="I50" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J50" s="32" t="s">
-        <v>169</v>
+      <c r="I50" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K50" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:13" ht="38.1" customHeight="1">
       <c r="A51" s="32" t="s">
@@ -6202,17 +6376,25 @@
       <c r="H51" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="I51" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J51" s="32" t="s">
-        <v>169</v>
+      <c r="I51" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K51" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
+      <c r="M51" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="52" spans="1:13" ht="38.1" customHeight="1">
       <c r="A52" s="32" t="s">
@@ -6239,17 +6421,25 @@
       <c r="H52" s="32" t="s">
         <v>414</v>
       </c>
-      <c r="I52" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J52" s="32" t="s">
-        <v>169</v>
+      <c r="I52" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J52" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K52" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
+      <c r="M52" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_guards.py</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:13" ht="38.1" customHeight="1">
       <c r="A53" s="32" t="s">
@@ -6276,8 +6466,10 @@
       <c r="H53" s="32" t="s">
         <v>419</v>
       </c>
-      <c r="I53" s="32" t="s">
-        <v>326</v>
+      <c r="I53" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="J53" s="32" t="inlineStr">
         <is>
@@ -6319,17 +6511,25 @@
       <c r="H54" s="32" t="s">
         <v>426</v>
       </c>
-      <c r="I54" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J54" s="32" t="s">
-        <v>169</v>
+      <c r="I54" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J54" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K54" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="55" spans="1:13" ht="38.1" customHeight="1">
       <c r="A55" s="32" t="s">
@@ -6356,17 +6556,25 @@
       <c r="H55" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="I55" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J55" s="32" t="s">
-        <v>169</v>
+      <c r="I55" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J55" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K55" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="56" spans="1:13" ht="38.1" customHeight="1">
       <c r="A56" s="32" t="s">
@@ -6393,17 +6601,25 @@
       <c r="H56" s="32" t="s">
         <v>435</v>
       </c>
-      <c r="I56" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="J56" s="32" t="s">
-        <v>169</v>
+      <c r="I56" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J56" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K56" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_flows.py</t>
+        </is>
+      </c>
     </row>
     <row r="57" spans="1:13" ht="38.1" customHeight="1">
       <c r="A57" s="32" t="s">
@@ -6430,17 +6646,25 @@
       <c r="H57" s="32" t="s">
         <v>441</v>
       </c>
-      <c r="I57" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="J57" s="32" t="s">
-        <v>169</v>
+      <c r="I57" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J57" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K57" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
+      <c r="M57" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_load.py</t>
+        </is>
+      </c>
     </row>
     <row r="58" spans="1:13" ht="38.1" customHeight="1">
       <c r="A58" s="32" t="s">
@@ -6467,17 +6691,25 @@
       <c r="H58" s="32" t="s">
         <v>446</v>
       </c>
-      <c r="I58" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="J58" s="32" t="s">
-        <v>169</v>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J58" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K58" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
+      <c r="M58" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_load.py</t>
+        </is>
+      </c>
     </row>
     <row r="59" spans="1:13" ht="38.1" customHeight="1">
       <c r="A59" s="32" t="s">
@@ -6504,17 +6736,25 @@
       <c r="H59" s="32" t="s">
         <v>452</v>
       </c>
-      <c r="I59" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="J59" s="32" t="s">
-        <v>169</v>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
       <c r="K59" s="32" t="s">
         <v>170</v>
       </c>
       <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>test_matrix_load.py</t>
+        </is>
+      </c>
     </row>
     <row r="60" spans="1:13" ht="38.1" customHeight="1">
       <c r="A60" s="29"/>

--- a/Plan.xlsx
+++ b/Plan.xlsx
@@ -3871,17 +3871,21 @@
       <c r="G21" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>36</v>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Descoped</t>
+        </is>
       </c>
       <c r="I21" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="K21" s="16" t="s">
-        <v>136</v>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>Bỏ deploy theo quyết định; seed/reset vẫn có, chạy local</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1">
@@ -3907,11 +3911,13 @@
       <c r="G22" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>36</v>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="I22" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>141</v>
